--- a/data/trans_orig/Q5418_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de lavarse la ropa en 2023</t>
+          <t>Población según si es capaz de lavarse la ropa en 2023 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10372</t>
+          <t>11140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>37332</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48431</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>46107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55567</t>
+          <t>55383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87665</t>
+          <t>87071</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101453</t>
+          <t>101120</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>12366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>30905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>12964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>27035</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63171</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>74656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89218</t>
+          <t>87545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104007</t>
+          <t>103314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156842</t>
+          <t>156830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175342</t>
+          <t>175721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22982</t>
+          <t>23189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20977</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>39787</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,47 +1770,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10516</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6954</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15240</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>12,03%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10516</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7102</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15948</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47938</t>
+          <t>47986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59843</t>
+          <t>59651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54780</t>
+          <t>54834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67282</t>
+          <t>67209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107334</t>
+          <t>107209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123541</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55747</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66236</t>
+          <t>66231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80394</t>
+          <t>79960</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>89994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139667</t>
+          <t>139773</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153717</t>
+          <t>153702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7027</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31393</t>
+          <t>31583</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51107</t>
+          <t>51116</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>71794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80727</t>
+          <t>80776</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,88%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>9656</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>35029</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>44523</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35913</t>
+          <t>36228</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45481</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74586</t>
+          <t>74001</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>88176</t>
+          <t>87760</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44596</t>
+          <t>42010</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6253</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33614</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>104672</t>
+          <t>105354</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116571</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>270277</t>
+          <t>271858</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>332008</t>
+          <t>332630</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>390975</t>
+          <t>392325</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>451039</t>
+          <t>449762</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,82 +3937,82 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>5217</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>2342</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>9663</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>7210</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>4218</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>12199</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>2361</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>9431</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>7210</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>12492</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12539</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>31346</t>
+          <t>30424</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23885</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>38303</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>130300</t>
+          <t>130609</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>139498</t>
+          <t>139777</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>150123</t>
+          <t>150371</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>164553</t>
+          <t>165228</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284444</t>
+          <t>284414</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>301917</t>
+          <t>302348</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>41246</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>62975</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>111061</t>
+          <t>110724</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>89158</t>
+          <t>90294</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>162603</t>
+          <t>163767</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>61915</t>
+          <t>61651</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>50241</t>
+          <t>48469</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>119590</t>
+          <t>119678</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>94743</t>
+          <t>92739</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>168004</t>
+          <t>167801</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>531462</t>
+          <t>530481</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>560694</t>
+          <t>558940</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>805647</t>
+          <t>805362</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>933379</t>
+          <t>937782</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1354839</t>
+          <t>1353126</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1495055</t>
+          <t>1496653</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5418_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11140</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43675</t>
+          <t>47672</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>41058</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48295</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51307</t>
+          <t>52929</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46107</t>
+          <t>47883</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55383</t>
+          <t>57109</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>94982</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87071</t>
+          <t>93040</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>106873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>27234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22747</t>
+          <t>24761</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>19384</t>
+          <t>20591</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12964</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70254</t>
+          <t>77145</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63293</t>
+          <t>69895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74656</t>
+          <t>81806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>96456</t>
+          <t>100274</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87545</t>
+          <t>91818</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103314</t>
+          <t>107568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>166710</t>
+          <t>177418</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>156830</t>
+          <t>166693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175721</t>
+          <t>187152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>208842</t>
+          <t>222771</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208842</t>
+          <t>222771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208842</t>
+          <t>222771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16932</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>20806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39787</t>
+          <t>39828</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15240</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13143</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54024</t>
+          <t>53214</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47986</t>
+          <t>46993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59651</t>
+          <t>58507</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>61817</t>
+          <t>59843</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54834</t>
+          <t>53612</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>65836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>115841</t>
+          <t>113057</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>107209</t>
+          <t>104447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123700</t>
+          <t>120900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,45%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>10016</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8546</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>18208</t>
+          <t>19125</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61265</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>62853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66231</t>
+          <t>73629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>85550</t>
+          <t>91442</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79960</t>
+          <t>86008</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89994</t>
+          <t>96318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>146815</t>
+          <t>160547</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>139773</t>
+          <t>152096</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153702</t>
+          <t>167502</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74084</t>
+          <t>82567</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74084</t>
+          <t>82567</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74084</t>
+          <t>82567</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>193071</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>193071</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>177720</t>
+          <t>193071</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>353</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>15282</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10992</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31583</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47839</t>
+          <t>49659</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43930</t>
+          <t>45361</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51116</t>
+          <t>53291</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>76652</t>
+          <t>80031</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71794</t>
+          <t>75029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80776</t>
+          <t>85194</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9656</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19756</t>
+          <t>20304</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35029</t>
+          <t>35631</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>21045</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>40365</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34971</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44523</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>41168</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>37493</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>47269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>81633</t>
+          <t>83244</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>87760</t>
+          <t>89435</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,13%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>19286</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>42010</t>
+          <t>28970</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>34327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12958</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>16146</t>
+          <t>19640</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>28871</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>111737</t>
+          <t>137419</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105354</t>
+          <t>129500</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>143400</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>314088</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>271858</t>
+          <t>124288</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>332630</t>
+          <t>141621</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>425826</t>
+          <t>270794</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>392325</t>
+          <t>258783</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>449762</t>
+          <t>281080</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4760</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12199</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4224</t>
+          <t>4751</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>27019</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>135769</t>
+          <t>150383</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>130609</t>
+          <t>143313</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>139777</t>
+          <t>154798</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>158119</t>
+          <t>179246</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>150371</t>
+          <t>170852</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>165228</t>
+          <t>187774</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>293887</t>
+          <t>329629</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>284414</t>
+          <t>318476</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>302348</t>
+          <t>339536</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>145239</t>
+          <t>161541</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>145239</t>
+          <t>161541</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>145239</t>
+          <t>161541</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>331881</t>
+          <t>374307</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>331881</t>
+          <t>374307</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>331881</t>
+          <t>374307</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>53288</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>43514</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>136607</t>
+          <t>146734</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>163767</t>
+          <t>166209</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>48469</t>
+          <t>85092</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>114949</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>92739</t>
+          <t>134890</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>167801</t>
+          <t>171005</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>546003</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>530481</t>
+          <t>589183</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>558940</t>
+          <t>620165</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>856345</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>691578</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>937782</t>
+          <t>728881</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1402348</t>
+          <t>1315322</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1353126</t>
+          <t>1290698</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1496653</t>
+          <t>1338615</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
